--- a/output/pdf_financials_xlsx/CURE.X.xlsx
+++ b/output/pdf_financials_xlsx/CURE.X.xlsx
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.004235</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.017949</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.041425</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.004235</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.017949</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.041425</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.004235</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.017949</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.042699</v>
+        <v>0.001274</v>
       </c>
     </row>
     <row r="49">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">

--- a/output/pdf_financials_xlsx/CURE.X.xlsx
+++ b/output/pdf_financials_xlsx/CURE.X.xlsx
@@ -1467,10 +1467,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.575972</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.348793</v>
       </c>
     </row>
     <row r="65">
@@ -1515,10 +1515,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.0275</v>
       </c>
     </row>
     <row r="68">
@@ -2206,10 +2206,10 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.007724</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.009121000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -3422,7 +3422,11 @@
           <t>Accretion expense 9</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
